--- a/artfynd/A 759-2024 artfynd.xlsx
+++ b/artfynd/A 759-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 759-2024 artfynd.xlsx
+++ b/artfynd/A 759-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113340728</v>
+        <v>113340710</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
+        <v>57624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,27 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -997,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113340710</v>
+        <v>113340704</v>
       </c>
       <c r="B5" t="n">
-        <v>57624</v>
+        <v>57281</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,20 +1031,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1126,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113340704</v>
+        <v>113340702</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
+        <v>57271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,16 +1145,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1234,116 +1237,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>113340702</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Plockepinnskogen, Väshult, Sm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>447955</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6353878</v>
-      </c>
-      <c r="S7" t="n">
-        <v>75</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Vaggeryd</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Hagshult</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mattias Bokinge</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mattias Bokinge</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
